--- a/Excel Projects/Project Report Summary.xlsx
+++ b/Excel Projects/Project Report Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80958CE2-2DC5-4CB3-8A58-43A61E8B5BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89006574-C67D-4A47-8A54-F7E722AB35DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4E903DBB-1DC7-4961-8993-54AAEF73C273}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Extracting Data From CSV</t>
   </si>
@@ -229,72 +229,6 @@
   </si>
   <si>
     <t>Hotel wise Total Booking and Cancellation</t>
-  </si>
-  <si>
-    <t>Hotel Wise Total  booking</t>
-  </si>
-  <si>
-    <t>Hotel wise booking cancalation</t>
-  </si>
-  <si>
-    <t>Month wise Hotel booking?</t>
-  </si>
-  <si>
-    <t>Hotel wise total guest?</t>
-  </si>
-  <si>
-    <t>Contry wise booking?</t>
-  </si>
-  <si>
-    <t>Hotel wise repeted guest?</t>
-  </si>
-  <si>
-    <t>Market segment wise total booking</t>
-  </si>
-  <si>
-    <t>Hotel wise previous cancalation</t>
-  </si>
-  <si>
-    <t>Hotel wise Satisfication?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel wise total booking &amp; cancalation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week day &amp; Weekend bookings </t>
-  </si>
-  <si>
-    <t>pick booking month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lead time vs booking </t>
-  </si>
-  <si>
-    <t>online vs offine booking</t>
-  </si>
-  <si>
-    <t>Hotel wise total revenue</t>
-  </si>
-  <si>
-    <t>market segmmet wise ADR</t>
-  </si>
-  <si>
-    <t>month wise ADR</t>
-  </si>
-  <si>
-    <t>cancalation revenue lose</t>
-  </si>
-  <si>
-    <t>AVG guests per booking</t>
-  </si>
-  <si>
-    <t>Hotel wise guest distibution</t>
-  </si>
-  <si>
-    <t>privious cancalation impact on new bookings</t>
-  </si>
-  <si>
-    <t>Which market segment wise ADR</t>
   </si>
   <si>
     <t>Weekday vs Weekend Bookings</t>
@@ -1179,307 +1113,199 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74503CBC-BC8F-4138-9AA5-53DE0700A16D}">
-  <dimension ref="B5:M28"/>
+  <dimension ref="B5:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>53</v>
       </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>54</v>
       </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
       </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>56</v>
       </c>
-      <c r="L8">
-        <v>4</v>
-      </c>
-      <c r="M8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>57</v>
       </c>
-      <c r="L9">
-        <v>5</v>
-      </c>
-      <c r="M9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10" t="s">
         <v>58</v>
       </c>
-      <c r="L10">
-        <v>6</v>
-      </c>
-      <c r="M10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="L11">
-        <v>7</v>
-      </c>
-      <c r="M11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="L12">
-        <v>8</v>
-      </c>
-      <c r="M12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>9</v>
       </c>
       <c r="C13" t="s">
         <v>60</v>
       </c>
-      <c r="L13">
-        <v>9</v>
-      </c>
-      <c r="M13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>61</v>
       </c>
-      <c r="L14">
-        <v>10</v>
-      </c>
-      <c r="M14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>11</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
       </c>
-      <c r="L15">
-        <v>11</v>
-      </c>
-      <c r="M15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>12</v>
       </c>
       <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="L16">
-        <v>12</v>
-      </c>
-      <c r="M16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
-      </c>
-      <c r="L17">
-        <v>13</v>
-      </c>
-      <c r="M17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18">
-        <v>14</v>
-      </c>
-      <c r="M18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="M20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="M21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="M22" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
-      </c>
-      <c r="M23" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="M24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="M25" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
-      </c>
-      <c r="M26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Excel Projects/Project Report Summary.xlsx
+++ b/Excel Projects/Project Report Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89006574-C67D-4A47-8A54-F7E722AB35DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D0B0FA-E8C5-4760-ACC7-FAA38FA3F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4E903DBB-1DC7-4961-8993-54AAEF73C273}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E903DBB-1DC7-4961-8993-54AAEF73C273}"/>
   </bookViews>
   <sheets>
     <sheet name="Cleaning Process &amp; Understand" sheetId="1" r:id="rId1"/>
